--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
@@ -51,15 +51,15 @@
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:51</t>
+    <t xml:space="preserve">2026-09-09 22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -601,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -627,7 +627,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2202</v>
+        <v>2302</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:39</t>
+    <t xml:space="preserve">2026-09-18 10:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ollagüe</t>
   </si>
   <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:01</t>
+    <t xml:space="preserve">2026-09-23 12:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -601,9 +601,11 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2202</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>2103</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
@@ -614,9 +616,11 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2103</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>2202</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
@@ -629,7 +633,9 @@
       <c r="C10" s="2" t="n">
         <v>2302</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E10" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:07</t>
+    <t xml:space="preserve">2026-10-02 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:34</t>
+    <t xml:space="preserve">2026-10-05 08:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
